--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/COXIM - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/COXIM - 24_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,42 +444,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7898676081439</t>
+          <t>7899248138926</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>JOGO BUCHA COROA CONTROLSEALS CG TITAN KS</t>
+          <t>JOGO COXIM COROA GP CBX250 TWISTER 1104106</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7898751863394</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JOGO BUCHA COROA EXTREMO CG TITAN</t>
+          <t>COXIM COROA ACLOPADO MJL CG TITAN150</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -490,117 +482,121 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7893986133816</t>
+          <t>7895098970242</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JOGO BUCHA COROA PECA+ BIZ100</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>JOGO COXIM COROA GOLDMOTOS BIZ100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7899248138926</t>
+          <t>751320981332</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JOGO COXIM COROA GP CBX250 TWISTER 1104106</t>
+          <t>JOGO COXIM COROA C100 BIZ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7895098972604</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>COXIM COROA ACLOPADO MJL CG TITAN150</t>
+          <t>JOGO COXIM COROA GOLDMOTOS BIZ125 20007</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7895098970242</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JOGO COXIM COROA GOLDMOTOS BIZ100</t>
+          <t>COXIM COROA ACOPLADO SUSUKI YES125/ INTRUDER125/ KATANA EN125</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>751320981332</t>
+          <t>7898590342586</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JOGO COXIM COROA C100 BIZ</t>
+          <t>JOGO COXIM COROA TRIBAL YBR 293</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7895098972604</t>
+          <t>7899468089374</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>JOGO COXIM COROA GOLDMOTOS BIZ125 20007</t>
+          <t>JOGO COXIM COROA TRILHA FAZER250 2005 A 2017</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -612,12 +608,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>COXIM COROA ACOPLADO SUSUKI YES125/ INTRUDER125/ KATANA EN125</t>
+          <t xml:space="preserve">COXIM COROA DORF SUSUKI </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -629,37 +629,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7898590342586</t>
+          <t>7899468011443</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JOGO COXIM COROA TRIBAL YBR 293</t>
+          <t>COXIM COROA ACLOPADO TRILHA YES125 2004 A 2012/ KATANA/ INTRUDER125 2002 A 2016</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7899468089374</t>
+          <t>6974288490409</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JOGO COXIM COROA TRILHA FAZER250 2005 A 2017</t>
+          <t>COXIM COROA ACLOPADO BRAVIC YES/ INTRUDER/ GSR BMA12002</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -671,196 +675,95 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t> </t>
+          <t>7898456463097</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">COXIM COROA DORF SUSUKI </t>
+          <t>JOGO COXIM COROA VEDOX FAZER 3068</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7899468011443</t>
+          <t>070341180549</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>COXIM COROA ACLOPADO TRILHA YES125 2004 A 2012/ KATANA/ INTRUDER125 2002 A 2016</t>
+          <t>JOGO COXIM COROA IRON DREAM/ TRAXX STAR-50/ CRYPTON/ SHINERAY 201975</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6974288490409</t>
+          <t>602883767157</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COXIM COROA ACLOPADO BRAVIC YES/ INTRUDER/ GSR BMA12002</t>
+          <t>JOGO COXIM COROA IRON CG TITAN150 2004 A 2015/ FAN150 2009 025520</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7898456463097</t>
+          <t>1234567890</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JOGO COXIM COROA VEDOX FAZER 3068</t>
+          <t>COXIM COROA YAMAHA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>070341180549</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>JOGO COXIM COROA IRON DREAM/ TRAXX STAR-50/ CRYPTON/ SHINERAY 201975</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>18</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>602883767157</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>JOGO COXIM COROA IRON CG TITAN150 2004 A 2015/ FAN150 2009 025520</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>19</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1234567890</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>COXIM COROA YAMAHA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>23</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>7893986507006</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>COXIM AMORTECEDOR TWISTER/ CB300/ XRE300/ TORNADO/ XR/ XLR</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>26</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>5637300001</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COXIM APOIO TANQUE  WR XTREME CG150 </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/COXIM - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/COXIM - 24_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -474,7 +468,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -495,11 +488,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,11 +508,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +528,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +544,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,7 +564,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -604,7 +584,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -625,7 +604,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -646,11 +624,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -671,7 +644,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -692,7 +664,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -713,11 +684,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -738,7 +704,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -757,11 +722,6 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
     </row>
